--- a/Projeto Controladoria Industrial.xlsx
+++ b/Projeto Controladoria Industrial.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" codeName="EstaPasta_de_trabalho" hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="5" activeTab="6"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="9" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Produtos" sheetId="1" r:id="rId1"/>
@@ -730,9 +730,9 @@
                       <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="pt-BR"/>
@@ -791,9 +791,9 @@
                       <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="pt-BR"/>
@@ -854,9 +854,9 @@
                       <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="pt-BR"/>
@@ -917,9 +917,9 @@
                       <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="pt-BR"/>
@@ -1094,9 +1094,9 @@
                         <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="pt-BR"/>
@@ -1183,6 +1183,47 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.69460663229279085"/>
+          <c:y val="2.5153955845781284E-2"/>
+          <c:w val="0.28678084655661695"/>
+          <c:h val="0.27902515681489964"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1221,6 +1262,7 @@
     <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
       <c14:pivotOptions>
         <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
         <c14:dropZoneSeries val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
@@ -2475,11 +2517,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="767246624"/>
-        <c:axId val="767246080"/>
+        <c:axId val="-1807111760"/>
+        <c:axId val="-1807101424"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="767246624"/>
+        <c:axId val="-1807111760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2522,7 +2564,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="767246080"/>
+        <c:crossAx val="-1807101424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2530,7 +2572,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="767246080"/>
+        <c:axId val="-1807101424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2581,7 +2623,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="767246624"/>
+        <c:crossAx val="-1807111760"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3132,8 +3174,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.35647952103533886"/>
-          <c:y val="5.7599985372122575E-2"/>
+          <c:x val="0.35647950548237545"/>
+          <c:y val="5.7600046131616227E-2"/>
           <c:w val="0.64352050121657012"/>
           <c:h val="0.94160985587271684"/>
         </c:manualLayout>
@@ -3299,11 +3341,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="767240096"/>
-        <c:axId val="767247168"/>
+        <c:axId val="-1807105776"/>
+        <c:axId val="-1807107952"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="767240096"/>
+        <c:axId val="-1807105776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3346,7 +3388,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="767247168"/>
+        <c:crossAx val="-1807107952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3354,7 +3396,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="767247168"/>
+        <c:axId val="-1807107952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3378,7 +3420,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="767240096"/>
+        <c:crossAx val="-1807105776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5657,15 +5699,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1524000</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>169027</xdr:rowOff>
+      <xdr:colOff>1409700</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>133351</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5718,16 +5760,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>46736</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>84836</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5750,16 +5792,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>146509</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>241759</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
